--- a/Results/tables/05b_monthly_article_flow.xlsx
+++ b/Results/tables/05b_monthly_article_flow.xlsx
@@ -1,37 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>Fiscal</t>
+  </si>
+  <si>
+    <t>Monetary</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +68,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -412,1266 +363,1252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fiscal</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Monetary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
         <v>43983</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>228</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>129</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>97</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>125</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
         <v>44013</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>753</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>386</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>354</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>400</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
         <v>44044</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>664</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>382</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>327</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>419</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
         <v>44075</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>731</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>361</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>334</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>452</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
         <v>44105</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>752</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>413</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>286</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>442</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
         <v>44136</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>718</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>413</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>321</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>421</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
         <v>44166</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1007</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>476</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>377</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>470</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
         <v>44197</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1123</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>614</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>395</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>552</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
         <v>44228</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1014</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>522</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>423</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>593</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
         <v>44256</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1109</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>591</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>444</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>665</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
         <v>44287</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>902</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>498</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>410</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>571</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
         <v>44317</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>714</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>408</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>347</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>433</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
         <v>44348</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>908</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>455</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>507</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>562</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
         <v>44378</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>692</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>297</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>319</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>378</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
         <v>44409</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>785</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>389</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>289</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>455</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
         <v>44440</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>867</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>353</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>343</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>505</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
         <v>44470</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>1001</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>417</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>307</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>510</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
         <v>44501</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>944</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>416</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>294</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>642</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
         <v>44531</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>930</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>471</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>303</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>584</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
         <v>44562</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>1026</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>464</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>340</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>752</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
         <v>44593</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>981</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>416</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>295</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>585</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
         <v>44621</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>1165</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>431</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>305</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>545</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
         <v>44652</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>810</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>406</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>274</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>573</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
         <v>44682</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>929</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>519</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>357</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>687</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
         <v>44713</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>1033</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>565</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>502</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>749</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
         <v>44743</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>805</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>471</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>267</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>703</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
         <v>44774</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>764</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>476</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>258</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>703</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
         <v>44805</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>701</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>487</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>243</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>708</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
         <v>44835</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>760</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>465</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>279</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>642</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
         <v>44866</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>671</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>360</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>247</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>636</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
         <v>44896</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>691</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>398</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>275</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>673</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
         <v>44927</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>756</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>500</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>301</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>748</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
         <v>44958</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>704</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>496</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>333</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>670</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
         <v>44986</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>730</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>494</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>348</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>705</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
         <v>45017</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>537</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>381</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>212</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>588</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
         <v>45047</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>681</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>482</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>331</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>587</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
         <v>45078</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>629</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>474</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>366</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>608</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
         <v>45108</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>672</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>549</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>263</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>634</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
         <v>45139</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>589</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>378</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>262</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>552</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
         <v>45170</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>617</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>360</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>221</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>513</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
         <v>45200</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>731</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>482</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>240</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>604</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
         <v>45231</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>668</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>439</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>207</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>617</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
         <v>45261</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>629</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>434</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>231</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>642</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
         <v>45292</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>720</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>456</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>272</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>722</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
         <v>45323</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>605</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>349</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>214</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>568</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
         <v>45352</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>640</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>454</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>242</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>612</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
         <v>45383</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>646</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>452</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>226</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>589</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
         <v>45413</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>682</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>460</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>312</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>698</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
         <v>45444</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>528</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>359</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>373</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>562</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
         <v>45474</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>621</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>424</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>362</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>611</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
         <v>45505</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>591</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>323</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>261</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>602</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
         <v>45536</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>592</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>470</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>254</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>735</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
         <v>45566</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>663</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>472</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>274</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>613</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
+    <row r="55" spans="1:5">
+      <c r="A55" s="1">
         <v>45597</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>618</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>434</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>230</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>521</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
+    <row r="56" spans="1:5">
+      <c r="A56" s="1">
         <v>45627</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>649</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>453</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>228</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>717</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
         <v>45658</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>668</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>445</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>254</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>629</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
         <v>45689</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>614</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>436</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>262</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>475</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
         <v>45717</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>553</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>423</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>218</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>407</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
         <v>45748</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>718</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>500</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>243</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>469</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
         <v>45778</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>667</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>469</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>388</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>490</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
         <v>45809</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>745</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>414</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>465</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>480</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
         <v>45839</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>658</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>438</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>338</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>521</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
         <v>45870</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>572</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>356</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>267</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>554</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
+    <row r="65" spans="1:5">
+      <c r="A65" s="1">
         <v>45901</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>582</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>390</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>273</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>612</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
+    <row r="66" spans="1:5">
+      <c r="A66" s="1">
         <v>45931</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>660</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>499</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>264</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>501</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
+    <row r="67" spans="1:5">
+      <c r="A67" s="1">
         <v>45962</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>538</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>376</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>205</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>494</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
+    <row r="68" spans="1:5">
+      <c r="A68" s="1">
         <v>45992</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>699</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>502</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>251</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>624</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
+    <row r="69" spans="1:5">
+      <c r="A69" s="1">
         <v>46023</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>700</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>451</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>237</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>456</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
+    <row r="70" spans="1:5">
+      <c r="A70" s="1">
         <v>46054</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>580</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>361</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>238</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>384</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
+    <row r="71" spans="1:5">
+      <c r="A71" s="1">
         <v>46082</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>1222</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>428</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>257</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>454</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
+    <row r="72" spans="1:5">
+      <c r="A72" s="1">
         <v>46113</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>1092</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>608</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>230</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>432</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
+    <row r="73" spans="1:5">
+      <c r="A73" s="1">
         <v>46143</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>738</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>432</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>203</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>322</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>